--- a/271025_Results_Med/MNL/mnl_med_sincomunas_OR.xlsx
+++ b/271025_Results_Med/MNL/mnl_med_sincomunas_OR.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -413,10 +413,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>-2.427</v>
+        <v>-2.437</v>
       </c>
       <c r="G2">
-        <v>0.0152</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="3">
@@ -431,19 +431,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>4.712</v>
+        <v>7.282</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E3">
-        <v>462937.488</v>
+        <v>37575.449</v>
       </c>
       <c r="F3">
-        <v>0.264</v>
+        <v>0.455</v>
       </c>
       <c r="G3">
-        <v>0.7915</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="4">
@@ -458,19 +458,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>87.25</v>
+        <v>74.005</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>541565257.512</v>
+        <v>17936035.658</v>
       </c>
       <c r="F4">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="G4">
-        <v>0.5755</v>
+        <v>0.4962</v>
       </c>
     </row>
     <row r="5">
@@ -481,23 +481,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="C5">
-        <v>0.066</v>
+        <v>30113.717</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="E5">
-        <v>32628401343.779</v>
+        <v>273970116469.678</v>
       </c>
       <c r="F5">
-        <v>-0.198</v>
+        <v>1.261</v>
       </c>
       <c r="G5">
-        <v>0.8429</v>
+        <v>0.2071</v>
       </c>
     </row>
     <row r="6">
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>31733508.72</v>
+        <v>318117361.629</v>
       </c>
       <c r="D6">
-        <v>54.33</v>
+        <v>344.846</v>
       </c>
       <c r="E6">
-        <v>18535206892621.14</v>
+        <v>293460299018196.4</v>
       </c>
       <c r="F6">
-        <v>2.55</v>
+        <v>2.794</v>
       </c>
       <c r="G6">
-        <v>0.0108</v>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="7">
@@ -539,19 +539,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>317674076145.61</v>
+        <v>32282181154.437</v>
       </c>
       <c r="D7">
-        <v>3378.864</v>
+        <v>806.077</v>
       </c>
       <c r="E7">
-        <v>2.986708516505974E+19</v>
+        <v>1.29285288126543E+18</v>
       </c>
       <c r="F7">
-        <v>2.827</v>
+        <v>2.709</v>
       </c>
       <c r="G7">
-        <v>0.0047</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="8">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>21.323</v>
+        <v>7.888</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>51141797.38</v>
+        <v>149146.239</v>
       </c>
       <c r="F8">
-        <v>0.408</v>
+        <v>0.411</v>
       </c>
       <c r="G8">
-        <v>0.6831</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="9">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>1631250710.574</v>
+        <v>238175166.88</v>
       </c>
       <c r="D9">
-        <v>181.995</v>
+        <v>1104.86</v>
       </c>
       <c r="E9">
-        <v>1.462118837425025E+16</v>
+        <v>51343507531002.43</v>
       </c>
       <c r="F9">
-        <v>2.597</v>
+        <v>3.078</v>
       </c>
       <c r="G9">
-        <v>0.0094</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="10">
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>1939.383</v>
+        <v>12.961</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>257158234178.67</v>
+        <v>173097527.161</v>
       </c>
       <c r="F10">
-        <v>0.793</v>
+        <v>0.306</v>
       </c>
       <c r="G10">
-        <v>0.4276</v>
+        <v>0.7596000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.404</v>
+        <v>0.183</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>8922606728.915001</v>
+        <v>102310.157</v>
       </c>
       <c r="F11">
-        <v>-0.075</v>
+        <v>-0.251</v>
       </c>
       <c r="G11">
-        <v>0.9405</v>
+        <v>0.8014</v>
       </c>
     </row>
     <row r="12">
@@ -674,19 +674,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>9333.611000000001</v>
+        <v>135.965</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>309512436981.386</v>
+        <v>8201029366.408</v>
       </c>
       <c r="F12">
-        <v>1.035</v>
+        <v>0.537</v>
       </c>
       <c r="G12">
-        <v>0.3008</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="13">
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>23.409</v>
+        <v>0.03</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>7020373900274.434</v>
+        <v>12380775.021</v>
       </c>
       <c r="F13">
-        <v>0.234</v>
+        <v>-0.347</v>
       </c>
       <c r="G13">
-        <v>0.8151</v>
+        <v>0.7289</v>
       </c>
     </row>
     <row r="14">
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>498.886</v>
+        <v>805.696</v>
       </c>
       <c r="F14">
-        <v>-1.293</v>
+        <v>-1.224</v>
       </c>
       <c r="G14">
-        <v>0.1959</v>
+        <v>0.2211</v>
       </c>
     </row>
     <row r="15">
@@ -764,7 +764,7 @@
         <v>0.001</v>
       </c>
       <c r="F15">
-        <v>-5.495</v>
+        <v>-17.179</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>838214.02</v>
+        <v>65891807.553</v>
       </c>
       <c r="F16">
-        <v>-0.586</v>
+        <v>-0.43</v>
       </c>
       <c r="G16">
-        <v>0.5580000000000001</v>
+        <v>0.6672</v>
       </c>
     </row>
     <row r="17">
@@ -809,19 +809,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.594</v>
+        <v>0.042</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="E17">
-        <v>206067102281075.2</v>
+        <v>0.05</v>
       </c>
       <c r="F17">
-        <v>-0.031</v>
+        <v>-33.958</v>
       </c>
       <c r="G17">
-        <v>0.9756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -832,23 +832,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="C18">
-        <v>2.127</v>
+        <v>5393.784</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>2626046855.389</v>
+        <v>175957314626.75</v>
       </c>
       <c r="F18">
-        <v>0.07099999999999999</v>
+        <v>0.974</v>
       </c>
       <c r="G18">
-        <v>0.9437</v>
+        <v>0.3303</v>
       </c>
     </row>
     <row r="19">
@@ -859,23 +859,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
         </is>
       </c>
       <c r="C19">
-        <v>702475.066</v>
+        <v>261.277</v>
       </c>
       <c r="D19">
-        <v>5.807</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>84984950328.575</v>
+        <v>78707480310.604</v>
       </c>
       <c r="F19">
-        <v>2.255</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G19">
-        <v>0.0242</v>
+        <v>0.5763</v>
       </c>
     </row>
     <row r="20">
@@ -886,23 +886,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="C20">
-        <v>229.963</v>
+        <v>113.656</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>116819706701.42</v>
+        <v>41752267.371</v>
       </c>
       <c r="F20">
-        <v>0.532</v>
+        <v>0.724</v>
       </c>
       <c r="G20">
-        <v>0.5949</v>
+        <v>0.4691</v>
       </c>
     </row>
     <row r="21">
@@ -913,23 +913,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="C21">
-        <v>12813.462</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>3546813512913.779</v>
+        <v>1241145.956</v>
       </c>
       <c r="F21">
-        <v>0.954</v>
+        <v>-0.714</v>
       </c>
       <c r="G21">
-        <v>0.3403</v>
+        <v>0.4754</v>
       </c>
     </row>
     <row r="22">
@@ -940,23 +940,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="C22">
-        <v>0.08</v>
+        <v>2.455</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="E22">
-        <v>4136529.521</v>
+        <v>492.996</v>
       </c>
       <c r="F22">
-        <v>-0.279</v>
+        <v>0.332</v>
       </c>
       <c r="G22">
-        <v>0.7804</v>
+        <v>0.7399</v>
       </c>
     </row>
     <row r="23">
@@ -967,23 +967,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
+          <t>p28_importancia_comodidad</t>
         </is>
       </c>
       <c r="C23">
-        <v>3798.043</v>
+        <v>1.257</v>
       </c>
       <c r="D23">
         <v>0.001</v>
       </c>
       <c r="E23">
-        <v>16912613518.642</v>
+        <v>1183.174</v>
       </c>
       <c r="F23">
-        <v>1.055</v>
+        <v>0.065</v>
       </c>
       <c r="G23">
-        <v>0.2913</v>
+        <v>0.9478</v>
       </c>
     </row>
     <row r="24">
@@ -994,23 +994,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+          <t>p28_importancia_costo_compra</t>
         </is>
       </c>
       <c r="C24">
-        <v>1545.852</v>
+        <v>3.151</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="E24">
-        <v>81433683159919</v>
+        <v>54.678</v>
       </c>
       <c r="F24">
-        <v>0.583</v>
+        <v>0.788</v>
       </c>
       <c r="G24">
-        <v>0.5599</v>
+        <v>0.4306</v>
       </c>
     </row>
     <row r="25">
@@ -1021,23 +1021,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>p23_agregado_Estudio</t>
+          <t>p28_importancia_costo_uso</t>
         </is>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="E25">
-        <v>193115.597</v>
+        <v>3.761</v>
       </c>
       <c r="F25">
-        <v>-0.763</v>
+        <v>-1.142</v>
       </c>
       <c r="G25">
-        <v>0.4455</v>
+        <v>0.2534</v>
       </c>
     </row>
     <row r="26">
@@ -1048,23 +1048,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p28_importancia_discriminacion</t>
         </is>
       </c>
       <c r="C26">
-        <v>1.561</v>
+        <v>0.367</v>
       </c>
       <c r="D26">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="E26">
-        <v>2963.845</v>
+        <v>8.18</v>
       </c>
       <c r="F26">
-        <v>0.116</v>
+        <v>-0.633</v>
       </c>
       <c r="G26">
-        <v>0.9079</v>
+        <v>0.5268</v>
       </c>
     </row>
     <row r="27">
@@ -1075,23 +1075,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>p28_importancia_comodidad</t>
+          <t>p28_importancia_emisiones</t>
         </is>
       </c>
       <c r="C27">
-        <v>0.439</v>
+        <v>7.763</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="E27">
-        <v>808.345</v>
+        <v>469.222</v>
       </c>
       <c r="F27">
-        <v>-0.215</v>
+        <v>0.979</v>
       </c>
       <c r="G27">
-        <v>0.8302</v>
+        <v>0.3274</v>
       </c>
     </row>
     <row r="28">
@@ -1102,23 +1102,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_compra</t>
+          <t>p28_importancia_riesgo_acoso</t>
         </is>
       </c>
       <c r="C28">
-        <v>5.268</v>
+        <v>0.15</v>
       </c>
       <c r="D28">
-        <v>0.117</v>
+        <v>0.005</v>
       </c>
       <c r="E28">
-        <v>236.625</v>
+        <v>4.889</v>
       </c>
       <c r="F28">
-        <v>0.856</v>
+        <v>-1.067</v>
       </c>
       <c r="G28">
-        <v>0.392</v>
+        <v>0.2859</v>
       </c>
     </row>
     <row r="29">
@@ -1129,23 +1129,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_uso</t>
+          <t>p28_importancia_riesgo_robo</t>
         </is>
       </c>
       <c r="C29">
-        <v>0.307</v>
+        <v>42.15</v>
       </c>
       <c r="D29">
-        <v>0.003</v>
+        <v>0.078</v>
       </c>
       <c r="E29">
-        <v>36.625</v>
+        <v>22732.065</v>
       </c>
       <c r="F29">
-        <v>-0.485</v>
+        <v>1.166</v>
       </c>
       <c r="G29">
-        <v>0.628</v>
+        <v>0.2437</v>
       </c>
     </row>
     <row r="30">
@@ -1156,23 +1156,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>p28_importancia_discriminacion</t>
+          <t>p28_importancia_siniestralidad</t>
         </is>
       </c>
       <c r="C30">
-        <v>0.285</v>
+        <v>0.102</v>
       </c>
       <c r="D30">
         <v>0.003</v>
       </c>
       <c r="E30">
-        <v>25.869</v>
+        <v>3.884</v>
       </c>
       <c r="F30">
-        <v>-0.546</v>
+        <v>-1.229</v>
       </c>
       <c r="G30">
-        <v>0.585</v>
+        <v>0.2191</v>
       </c>
     </row>
     <row r="31">
@@ -1183,23 +1183,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>p28_importancia_emisiones</t>
+          <t>p28_importancia_tiempo</t>
         </is>
       </c>
       <c r="C31">
-        <v>11.35</v>
+        <v>1.485</v>
       </c>
       <c r="D31">
-        <v>0.068</v>
+        <v>0.012</v>
       </c>
       <c r="E31">
-        <v>1888.152</v>
+        <v>177.185</v>
       </c>
       <c r="F31">
-        <v>0.931</v>
+        <v>0.162</v>
       </c>
       <c r="G31">
-        <v>0.3518</v>
+        <v>0.8711</v>
       </c>
     </row>
     <row r="32">
@@ -1210,23 +1210,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_acoso</t>
+          <t>p32_contaminacion_likert</t>
         </is>
       </c>
       <c r="C32">
-        <v>0.294</v>
+        <v>77.504</v>
       </c>
       <c r="D32">
-        <v>0.004</v>
+        <v>0.122</v>
       </c>
       <c r="E32">
-        <v>21.083</v>
+        <v>49290.574</v>
       </c>
       <c r="F32">
-        <v>-0.5620000000000001</v>
+        <v>1.321</v>
       </c>
       <c r="G32">
-        <v>0.5741000000000001</v>
+        <v>0.1865</v>
       </c>
     </row>
     <row r="33">
@@ -1237,23 +1237,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_robo</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="C33">
-        <v>23.194</v>
+        <v>16.762</v>
       </c>
       <c r="D33">
-        <v>0.062</v>
+        <v>0.002</v>
       </c>
       <c r="E33">
-        <v>8666.965</v>
+        <v>172917.602</v>
       </c>
       <c r="F33">
-        <v>1.04</v>
+        <v>0.598</v>
       </c>
       <c r="G33">
-        <v>0.2982</v>
+        <v>0.5499000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1264,23 +1264,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>p28_importancia_siniestralidad</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="C34">
-        <v>0.042</v>
+        <v>0.74</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>7.666</v>
+        <v>186800.392</v>
       </c>
       <c r="F34">
-        <v>-1.192</v>
+        <v>-0.047</v>
       </c>
       <c r="G34">
-        <v>0.2334</v>
+        <v>0.9622000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1291,23 +1291,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>p28_importancia_tiempo</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="C35">
-        <v>1.929</v>
+        <v>73.678</v>
       </c>
       <c r="D35">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
       <c r="E35">
-        <v>384.601</v>
+        <v>283196.197</v>
       </c>
       <c r="F35">
-        <v>0.243</v>
+        <v>1.021</v>
       </c>
       <c r="G35">
-        <v>0.8079</v>
+        <v>0.3073</v>
       </c>
     </row>
     <row r="36">
@@ -1318,23 +1318,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>p32_contaminacion_likert</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="C36">
-        <v>17.387</v>
+        <v>70303.44100000001</v>
       </c>
       <c r="D36">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="E36">
-        <v>13329.479</v>
+        <v>1332154819255.124</v>
       </c>
       <c r="F36">
-        <v>0.843</v>
+        <v>1.305</v>
       </c>
       <c r="G36">
-        <v>0.3994</v>
+        <v>0.1918</v>
       </c>
     </row>
     <row r="37">
@@ -1345,23 +1345,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>p36_influencia_amigos</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="C37">
-        <v>4.864</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>340.058</v>
+        <v>18.442</v>
       </c>
       <c r="F37">
-        <v>0.73</v>
+        <v>-1.525</v>
       </c>
       <c r="G37">
-        <v>0.4654</v>
+        <v>0.1273</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>p37_influencia_familia</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="C38">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>3.824</v>
+        <v>6.522</v>
       </c>
       <c r="F38">
-        <v>-1.221</v>
+        <v>-1.672</v>
       </c>
       <c r="G38">
-        <v>0.222</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="39">
@@ -1399,185 +1399,185 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>p38p38_dummy_1</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="C39">
-        <v>118.479</v>
+        <v>1.009</v>
       </c>
       <c r="D39">
-        <v>0.001</v>
+        <v>0.728</v>
       </c>
       <c r="E39">
-        <v>10445869.148</v>
+        <v>1.397</v>
       </c>
       <c r="F39">
-        <v>0.822</v>
+        <v>0.053</v>
       </c>
       <c r="G39">
-        <v>0.4112</v>
+        <v>0.9578</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>p40_Mujer</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="C40">
-        <v>82.251</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>4885201.975</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>0.786</v>
+        <v>-7.519</v>
       </c>
       <c r="G40">
-        <v>0.4317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>p5_agregado_Secundaria</t>
+          <t>`edad_r2_18 - 34 años`</t>
         </is>
       </c>
       <c r="C41">
-        <v>39.799</v>
+        <v>1.573</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="E41">
-        <v>84234143.25300001</v>
+        <v>57.109</v>
       </c>
       <c r="F41">
-        <v>0.496</v>
+        <v>0.247</v>
       </c>
       <c r="G41">
-        <v>0.6201</v>
+        <v>0.8048</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>p7_agregado_Estudiante</t>
+          <t>`edad_r2_55 - 80 años`</t>
         </is>
       </c>
       <c r="C42">
-        <v>2459301.266</v>
+        <v>350.639</v>
       </c>
       <c r="D42">
-        <v>0.106</v>
+        <v>4.649</v>
       </c>
       <c r="E42">
-        <v>57028057366432.7</v>
+        <v>26448.176</v>
       </c>
       <c r="F42">
-        <v>1.701</v>
+        <v>2.657</v>
       </c>
       <c r="G42">
-        <v>0.089</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>p9_estrato3_Bajo</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1192.181</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2.458</v>
       </c>
       <c r="E43">
-        <v>3.001</v>
+        <v>578288.1360000001</v>
       </c>
       <c r="F43">
-        <v>-1.79</v>
+        <v>2.245</v>
       </c>
       <c r="G43">
-        <v>0.0735</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>p9_estrato3_Medio</t>
+          <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="E44">
-        <v>108.96</v>
+        <v>497.33</v>
       </c>
       <c r="F44">
-        <v>-1.311</v>
+        <v>0.998</v>
       </c>
       <c r="G44">
-        <v>0.1899</v>
+        <v>0.3184</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Auto privado</t>
+          <t>Modo activo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>tiempo_total</t>
+          <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
       <c r="C45">
-        <v>1.051</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>1.459</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>0.298</v>
+        <v>-27222.845</v>
       </c>
       <c r="G45">
-        <v>0.7659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1588,23 +1588,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>`p16_motos_agregado_1 motocicleta`</t>
         </is>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>813295.889</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>17501.005</v>
       </c>
       <c r="E46">
-        <v>3.889</v>
+        <v>37794983.25</v>
       </c>
       <c r="F46">
-        <v>-1.828</v>
+        <v>6.948</v>
       </c>
       <c r="G46">
-        <v>0.06759999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1615,23 +1615,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>`edad_r2_18 - 34 años`</t>
+          <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
       <c r="C47">
-        <v>0.43</v>
+        <v>8789783249.187</v>
       </c>
       <c r="D47">
-        <v>0.002</v>
+        <v>83899491.473</v>
       </c>
       <c r="E47">
-        <v>95.569</v>
+        <v>920867197305.91</v>
       </c>
       <c r="F47">
-        <v>-0.306</v>
+        <v>9.648</v>
       </c>
       <c r="G47">
-        <v>0.7593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1642,23 +1642,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>`edad_r2_55 - 80 años`</t>
+          <t>`p22_Entre 11 y 15 km`</t>
         </is>
       </c>
       <c r="C48">
-        <v>2399.345</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>3.125</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>1842254.759</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>2.296</v>
+        <v>-57429.652</v>
       </c>
       <c r="G48">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1669,23 +1669,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`p22_Entre 16 y 20 km`</t>
         </is>
       </c>
       <c r="C49">
-        <v>17.087</v>
+        <v>15652783.701</v>
       </c>
       <c r="D49">
-        <v>0.089</v>
+        <v>534556.3370000001</v>
       </c>
       <c r="E49">
-        <v>3285.087</v>
+        <v>458342031.577</v>
       </c>
       <c r="F49">
-        <v>1.058</v>
+        <v>9.615</v>
       </c>
       <c r="G49">
-        <v>0.2901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1696,23 +1696,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_1 auto`</t>
+          <t>`p22_Entre 6 y 10 km`</t>
         </is>
       </c>
       <c r="C50">
-        <v>93.777</v>
+        <v>642543.096</v>
       </c>
       <c r="D50">
-        <v>0.305</v>
+        <v>20705.561</v>
       </c>
       <c r="E50">
-        <v>28799.275</v>
+        <v>19939649.148</v>
       </c>
       <c r="F50">
-        <v>1.554</v>
+        <v>7.631</v>
       </c>
       <c r="G50">
-        <v>0.1202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1723,20 +1723,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_2 o más autos`</t>
+          <t>`p22_Menos de 5 km`</t>
         </is>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>126296438.385</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>4272200.174</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>3733624291.987</v>
       </c>
       <c r="F51">
-        <v>-49020.313</v>
+        <v>10.796</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -1750,23 +1750,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_1 motocicleta`</t>
+          <t>`p23_agregado_Compras y trámites`</t>
         </is>
       </c>
       <c r="C52">
-        <v>374763.834</v>
+        <v>0.329</v>
       </c>
       <c r="D52">
-        <v>0.077</v>
+        <v>0.002</v>
       </c>
       <c r="E52">
-        <v>1831915865908.982</v>
+        <v>47.98</v>
       </c>
       <c r="F52">
-        <v>1.633</v>
+        <v>-0.438</v>
       </c>
       <c r="G52">
-        <v>0.1024</v>
+        <v>0.6617</v>
       </c>
     </row>
     <row r="53">
@@ -1777,23 +1777,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_Sin motocicletas`</t>
+          <t>`p23_agregado_Cuidado y familia`</t>
         </is>
       </c>
       <c r="C53">
-        <v>6358846200.771</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1334.462</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>3.030053486774766E+16</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>2.877</v>
+        <v>-68170.539</v>
       </c>
       <c r="G53">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1804,23 +1804,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>`p22_Entre 11 y 15 km`</t>
+          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
         </is>
       </c>
       <c r="C54">
-        <v>0.038</v>
+        <v>3.953</v>
       </c>
       <c r="D54">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="E54">
-        <v>0.242</v>
+        <v>550.2190000000001</v>
       </c>
       <c r="F54">
-        <v>-3.461</v>
+        <v>0.546</v>
       </c>
       <c r="G54">
-        <v>0.0005</v>
+        <v>0.5852000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -1831,23 +1831,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>`p22_Entre 16 y 20 km`</t>
+          <t>`p23_agregado_Visitas sociales`</t>
         </is>
       </c>
       <c r="C55">
-        <v>165987.919</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>145906461777.317</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>1.721</v>
+        <v>-192.552</v>
       </c>
       <c r="G55">
-        <v>0.0852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1858,23 +1858,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>`p22_Entre 6 y 10 km`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="C56">
-        <v>4086.136</v>
+        <v>0.701</v>
       </c>
       <c r="D56">
-        <v>0.017</v>
+        <v>0.001</v>
       </c>
       <c r="E56">
-        <v>965096353.359</v>
+        <v>780.898</v>
       </c>
       <c r="F56">
-        <v>1.317</v>
+        <v>-0.099</v>
       </c>
       <c r="G56">
-        <v>0.1877</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -1885,23 +1885,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>`p22_Menos de 5 km`</t>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
         </is>
       </c>
       <c r="C57">
-        <v>1567532.147</v>
+        <v>0.366</v>
       </c>
       <c r="D57">
-        <v>2.825</v>
+        <v>0.001</v>
       </c>
       <c r="E57">
-        <v>869888614872.547</v>
+        <v>227.313</v>
       </c>
       <c r="F57">
-        <v>2.114</v>
+        <v>-0.306</v>
       </c>
       <c r="G57">
-        <v>0.0345</v>
+        <v>0.7594</v>
       </c>
     </row>
     <row r="58">
@@ -1912,23 +1912,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>`p23_agregado_Compras y trámites`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="C58">
-        <v>0.076</v>
+        <v>10.31</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="E58">
-        <v>61.019</v>
+        <v>737.352</v>
       </c>
       <c r="F58">
-        <v>-0.755</v>
+        <v>1.071</v>
       </c>
       <c r="G58">
-        <v>0.4505</v>
+        <v>0.2842</v>
       </c>
     </row>
     <row r="59">
@@ -1939,23 +1939,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>`p23_agregado_Cuidado y familia`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>0.113</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>1111.755</v>
       </c>
       <c r="F59">
-        <v>-375.323</v>
+        <v>-0.464</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>0.6425</v>
       </c>
     </row>
     <row r="60">
@@ -1966,23 +1966,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="C60">
-        <v>0.07199999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="E60">
-        <v>418.387</v>
+        <v>0.651</v>
       </c>
       <c r="F60">
-        <v>-0.594</v>
+        <v>-2.43</v>
       </c>
       <c r="G60">
-        <v>0.5523</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="61">
@@ -1993,23 +1993,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>`p23_agregado_Visitas sociales`</t>
+          <t>p28_importancia_comodidad</t>
         </is>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="E61">
-        <v>749470306.414</v>
+        <v>1.494</v>
       </c>
       <c r="F61">
-        <v>-0.725</v>
+        <v>-1.615</v>
       </c>
       <c r="G61">
-        <v>0.4683</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="62">
@@ -2020,23 +2020,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>p28_importancia_costo_compra</t>
         </is>
       </c>
       <c r="C62">
-        <v>31.968</v>
+        <v>6.48</v>
       </c>
       <c r="D62">
-        <v>0.077</v>
+        <v>1.459</v>
       </c>
       <c r="E62">
-        <v>13289.806</v>
+        <v>28.782</v>
       </c>
       <c r="F62">
-        <v>1.126</v>
+        <v>2.456</v>
       </c>
       <c r="G62">
-        <v>0.2601</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="63">
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>p28_importancia_costo_uso</t>
         </is>
       </c>
       <c r="C63">
-        <v>111.347</v>
+        <v>0.529</v>
       </c>
       <c r="D63">
-        <v>0.003</v>
+        <v>0.167</v>
       </c>
       <c r="E63">
-        <v>4570248.008</v>
+        <v>1.675</v>
       </c>
       <c r="F63">
-        <v>0.87</v>
+        <v>-1.083</v>
       </c>
       <c r="G63">
-        <v>0.3845</v>
+        <v>0.2786</v>
       </c>
     </row>
     <row r="64">
@@ -2074,23 +2074,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>p28_importancia_discriminacion</t>
         </is>
       </c>
       <c r="C64">
-        <v>1.752</v>
+        <v>0.367</v>
       </c>
       <c r="D64">
-        <v>0.002</v>
+        <v>0.099</v>
       </c>
       <c r="E64">
-        <v>1414.146</v>
+        <v>1.365</v>
       </c>
       <c r="F64">
-        <v>0.164</v>
+        <v>-1.495</v>
       </c>
       <c r="G64">
-        <v>0.8696</v>
+        <v>0.1348</v>
       </c>
     </row>
     <row r="65">
@@ -2101,23 +2101,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
+          <t>p28_importancia_emisiones</t>
         </is>
       </c>
       <c r="C65">
-        <v>47041.96</v>
+        <v>5.337</v>
       </c>
       <c r="D65">
-        <v>0.093</v>
+        <v>1.141</v>
       </c>
       <c r="E65">
-        <v>23685938801.037</v>
+        <v>24.974</v>
       </c>
       <c r="F65">
-        <v>1.606</v>
+        <v>2.127</v>
       </c>
       <c r="G65">
-        <v>0.1082</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="66">
@@ -2128,23 +2128,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>p28_importancia_riesgo_acoso</t>
         </is>
       </c>
       <c r="C66">
-        <v>12.632</v>
+        <v>1.044</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>0.254</v>
       </c>
       <c r="E66">
-        <v>70392425.089</v>
+        <v>4.295</v>
       </c>
       <c r="F66">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="G66">
-        <v>0.749</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="67">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
+          <t>p28_importancia_riesgo_robo</t>
         </is>
       </c>
       <c r="C67">
-        <v>0.124</v>
+        <v>1.588</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="E67">
-        <v>1597.716</v>
+        <v>5.393</v>
       </c>
       <c r="F67">
-        <v>-0.432</v>
+        <v>0.741</v>
       </c>
       <c r="G67">
-        <v>0.6657</v>
+        <v>0.4588</v>
       </c>
     </row>
     <row r="68">
@@ -2182,23 +2182,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+          <t>p28_importancia_siniestralidad</t>
         </is>
       </c>
       <c r="C68">
-        <v>19.246</v>
+        <v>0.446</v>
       </c>
       <c r="D68">
-        <v>0.004</v>
+        <v>0.125</v>
       </c>
       <c r="E68">
-        <v>96787.645</v>
+        <v>1.588</v>
       </c>
       <c r="F68">
-        <v>0.68</v>
+        <v>-1.246</v>
       </c>
       <c r="G68">
-        <v>0.4964</v>
+        <v>0.2128</v>
       </c>
     </row>
     <row r="69">
@@ -2209,23 +2209,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>p23_agregado_Estudio</t>
+          <t>p28_importancia_tiempo</t>
         </is>
       </c>
       <c r="C69">
-        <v>0.229</v>
+        <v>1.201</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="E69">
-        <v>1020431270275809</v>
+        <v>7.07</v>
       </c>
       <c r="F69">
-        <v>-0.08</v>
+        <v>0.203</v>
       </c>
       <c r="G69">
-        <v>0.9362</v>
+        <v>0.8394</v>
       </c>
     </row>
     <row r="70">
@@ -2236,23 +2236,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p32_contaminacion_likert</t>
         </is>
       </c>
       <c r="C70">
-        <v>0.065</v>
+        <v>0.159</v>
       </c>
       <c r="D70">
-        <v>0.006</v>
+        <v>0.037</v>
       </c>
       <c r="E70">
-        <v>0.736</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F70">
-        <v>-2.208</v>
+        <v>-2.475</v>
       </c>
       <c r="G70">
-        <v>0.0272</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="71">
@@ -2263,23 +2263,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>p28_importancia_comodidad</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="C71">
-        <v>0.07199999999999999</v>
+        <v>135.745</v>
       </c>
       <c r="D71">
-        <v>0.004</v>
+        <v>4.415</v>
       </c>
       <c r="E71">
-        <v>1.275</v>
+        <v>4173.462</v>
       </c>
       <c r="F71">
-        <v>-1.795</v>
+        <v>2.81</v>
       </c>
       <c r="G71">
-        <v>0.0727</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="72">
@@ -2290,23 +2290,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_compra</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="C72">
-        <v>11.099</v>
+        <v>10.011</v>
       </c>
       <c r="D72">
-        <v>1.179</v>
+        <v>0.107</v>
       </c>
       <c r="E72">
-        <v>104.521</v>
+        <v>939.297</v>
       </c>
       <c r="F72">
-        <v>2.104</v>
+        <v>0.994</v>
       </c>
       <c r="G72">
-        <v>0.0354</v>
+        <v>0.3201</v>
       </c>
     </row>
     <row r="73">
@@ -2317,23 +2317,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_uso</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="C73">
-        <v>0.51</v>
+        <v>0.659</v>
       </c>
       <c r="D73">
-        <v>0.117</v>
+        <v>0.035</v>
       </c>
       <c r="E73">
-        <v>2.222</v>
+        <v>12.432</v>
       </c>
       <c r="F73">
-        <v>-0.897</v>
+        <v>-0.278</v>
       </c>
       <c r="G73">
-        <v>0.3699</v>
+        <v>0.7806999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -2344,23 +2344,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>p28_importancia_discriminacion</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="C74">
-        <v>0.173</v>
+        <v>131028.679</v>
       </c>
       <c r="D74">
-        <v>0.03</v>
+        <v>3.86</v>
       </c>
       <c r="E74">
-        <v>0.989</v>
+        <v>4447405896.571</v>
       </c>
       <c r="F74">
-        <v>-1.972</v>
+        <v>2.214</v>
       </c>
       <c r="G74">
-        <v>0.0486</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="75">
@@ -2371,23 +2371,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>p28_importancia_emisiones</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="C75">
-        <v>7.165</v>
+        <v>0.003</v>
       </c>
       <c r="D75">
-        <v>0.986</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>52.04</v>
+        <v>0.659</v>
       </c>
       <c r="F75">
-        <v>1.947</v>
+        <v>-2.115</v>
       </c>
       <c r="G75">
-        <v>0.0516</v>
+        <v>0.0344</v>
       </c>
     </row>
     <row r="76">
@@ -2398,23 +2398,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_acoso</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="C76">
-        <v>1.553</v>
+        <v>0.019</v>
       </c>
       <c r="D76">
-        <v>0.288</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>8.380000000000001</v>
+        <v>2.454</v>
       </c>
       <c r="F76">
-        <v>0.511</v>
+        <v>-1.6</v>
       </c>
       <c r="G76">
-        <v>0.609</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="77">
@@ -2425,347 +2425,347 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_robo</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="C77">
-        <v>2.126</v>
+        <v>1.175</v>
       </c>
       <c r="D77">
-        <v>0.35</v>
+        <v>1.076</v>
       </c>
       <c r="E77">
-        <v>12.897</v>
+        <v>1.282</v>
       </c>
       <c r="F77">
-        <v>0.82</v>
+        <v>3.594</v>
       </c>
       <c r="G77">
-        <v>0.4124</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>p28_importancia_siniestralidad</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="C78">
-        <v>0.282</v>
+        <v>0.044</v>
       </c>
       <c r="D78">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>1.408</v>
+        <v>791.946</v>
       </c>
       <c r="F78">
-        <v>-1.543</v>
+        <v>-0.626</v>
       </c>
       <c r="G78">
-        <v>0.1229</v>
+        <v>0.5314</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>p28_importancia_tiempo</t>
+          <t>`edad_r2_18 - 34 años`</t>
         </is>
       </c>
       <c r="C79">
-        <v>0.705</v>
+        <v>1.846</v>
       </c>
       <c r="D79">
-        <v>0.095</v>
+        <v>0.204</v>
       </c>
       <c r="E79">
-        <v>5.227</v>
+        <v>16.699</v>
       </c>
       <c r="F79">
-        <v>-0.342</v>
+        <v>0.546</v>
       </c>
       <c r="G79">
-        <v>0.7326</v>
+        <v>0.5853</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>p32_contaminacion_likert</t>
+          <t>`edad_r2_55 - 80 años`</t>
         </is>
       </c>
       <c r="C80">
-        <v>0.08500000000000001</v>
+        <v>5.237</v>
       </c>
       <c r="D80">
-        <v>0.008999999999999999</v>
+        <v>0.227</v>
       </c>
       <c r="E80">
-        <v>0.769</v>
+        <v>120.609</v>
       </c>
       <c r="F80">
-        <v>-2.193</v>
+        <v>1.035</v>
       </c>
       <c r="G80">
-        <v>0.0283</v>
+        <v>0.3009</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>p36_influencia_amigos</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="C81">
-        <v>1.044</v>
+        <v>2.716</v>
       </c>
       <c r="D81">
-        <v>0.15</v>
+        <v>0.067</v>
       </c>
       <c r="E81">
-        <v>7.242</v>
+        <v>109.979</v>
       </c>
       <c r="F81">
-        <v>0.043</v>
+        <v>0.529</v>
       </c>
       <c r="G81">
-        <v>0.9656</v>
+        <v>0.5968</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>p37_influencia_familia</t>
+          <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
       <c r="C82">
-        <v>1.791</v>
+        <v>5.079</v>
       </c>
       <c r="D82">
-        <v>0.271</v>
+        <v>0.41</v>
       </c>
       <c r="E82">
-        <v>11.837</v>
+        <v>62.984</v>
       </c>
       <c r="F82">
-        <v>0.605</v>
+        <v>1.265</v>
       </c>
       <c r="G82">
-        <v>0.5452</v>
+        <v>0.2059</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>p38p38_dummy_1</t>
+          <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
       <c r="C83">
-        <v>891.438</v>
+        <v>0.613</v>
       </c>
       <c r="D83">
-        <v>6.82</v>
+        <v>0.001</v>
       </c>
       <c r="E83">
-        <v>116519.733</v>
+        <v>363.63</v>
       </c>
       <c r="F83">
-        <v>2.732</v>
+        <v>-0.15</v>
       </c>
       <c r="G83">
-        <v>0.0063</v>
+        <v>0.8806</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>p40_Mujer</t>
+          <t>`p16_motos_agregado_1 motocicleta`</t>
         </is>
       </c>
       <c r="C84">
-        <v>0.35</v>
+        <v>0.319</v>
       </c>
       <c r="D84">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="E84">
-        <v>20.121</v>
+        <v>4.676</v>
       </c>
       <c r="F84">
-        <v>-0.508</v>
+        <v>-0.834</v>
       </c>
       <c r="G84">
-        <v>0.6118</v>
+        <v>0.4045</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>p5_agregado_Secundaria</t>
+          <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
       <c r="C85">
-        <v>1266.953</v>
+        <v>70525.49000000001</v>
       </c>
       <c r="D85">
-        <v>0.002</v>
+        <v>598.546</v>
       </c>
       <c r="E85">
-        <v>732008915.679</v>
+        <v>8309872.003</v>
       </c>
       <c r="F85">
-        <v>1.055</v>
+        <v>4.588</v>
       </c>
       <c r="G85">
-        <v>0.2912</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>p7_agregado_Estudiante</t>
+          <t>`p22_Entre 11 y 15 km`</t>
         </is>
       </c>
       <c r="C86">
-        <v>147113.85</v>
+        <v>1.972</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="E86">
-        <v>1.070671125082606E+21</v>
+        <v>114.6</v>
       </c>
       <c r="F86">
-        <v>0.639</v>
+        <v>0.328</v>
       </c>
       <c r="G86">
-        <v>0.5231</v>
+        <v>0.7432</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>p9_estrato3_Bajo</t>
+          <t>`p22_Entre 16 y 20 km`</t>
         </is>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>65.779</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>0.989</v>
       </c>
       <c r="E87">
-        <v>0.375</v>
+        <v>4373.402</v>
       </c>
       <c r="F87">
-        <v>-2.203</v>
+        <v>1.955</v>
       </c>
       <c r="G87">
-        <v>0.0276</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>p9_estrato3_Medio</t>
+          <t>`p22_Entre 6 y 10 km`</t>
         </is>
       </c>
       <c r="C88">
-        <v>0.002</v>
+        <v>35.431</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>0.604</v>
       </c>
       <c r="E88">
-        <v>1.832</v>
+        <v>2079.318</v>
       </c>
       <c r="F88">
-        <v>-1.788</v>
+        <v>1.717</v>
       </c>
       <c r="G88">
-        <v>0.0738</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Modo activo</t>
+          <t>Taxi / Plataforma</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>tiempo_total</t>
+          <t>`p22_Menos de 5 km`</t>
         </is>
       </c>
       <c r="C89">
-        <v>1.197</v>
+        <v>278.815</v>
       </c>
       <c r="D89">
-        <v>1.07</v>
+        <v>2.699</v>
       </c>
       <c r="E89">
-        <v>1.339</v>
+        <v>28806.622</v>
       </c>
       <c r="F89">
-        <v>3.151</v>
+        <v>2.38</v>
       </c>
       <c r="G89">
-        <v>0.0016</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="90">
@@ -2776,23 +2776,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>`p23_agregado_Compras y trámites`</t>
         </is>
       </c>
       <c r="C90">
-        <v>0.038</v>
+        <v>0.119</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E90">
-        <v>4226.145</v>
+        <v>6.447</v>
       </c>
       <c r="F90">
-        <v>-0.552</v>
+        <v>-1.046</v>
       </c>
       <c r="G90">
-        <v>0.5812</v>
+        <v>0.2956</v>
       </c>
     </row>
     <row r="91">
@@ -2803,23 +2803,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>`edad_r2_18 - 34 años`</t>
+          <t>`p23_agregado_Cuidado y familia`</t>
         </is>
       </c>
       <c r="C91">
-        <v>2.056</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>34.109</v>
+        <v>0.161</v>
       </c>
       <c r="F91">
-        <v>0.503</v>
+        <v>-2.488</v>
       </c>
       <c r="G91">
-        <v>0.615</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="92">
@@ -2830,23 +2830,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>`edad_r2_55 - 80 años`</t>
+          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
         </is>
       </c>
       <c r="C92">
-        <v>13.009</v>
+        <v>5.986</v>
       </c>
       <c r="D92">
-        <v>0.221</v>
+        <v>0.215</v>
       </c>
       <c r="E92">
-        <v>765.17</v>
+        <v>166.908</v>
       </c>
       <c r="F92">
-        <v>1.234</v>
+        <v>1.054</v>
       </c>
       <c r="G92">
-        <v>0.2171</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="93">
@@ -2857,23 +2857,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`p23_agregado_Visitas sociales`</t>
         </is>
       </c>
       <c r="C93">
-        <v>8.239000000000001</v>
+        <v>0.539</v>
       </c>
       <c r="D93">
-        <v>0.107</v>
+        <v>0.004</v>
       </c>
       <c r="E93">
-        <v>632.835</v>
+        <v>78.62</v>
       </c>
       <c r="F93">
-        <v>0.952</v>
+        <v>-0.243</v>
       </c>
       <c r="G93">
-        <v>0.341</v>
+        <v>0.8078</v>
       </c>
     </row>
     <row r="94">
@@ -2884,23 +2884,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_1 auto`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="C94">
-        <v>7.076</v>
+        <v>961.136</v>
       </c>
       <c r="D94">
-        <v>0.298</v>
+        <v>6.037</v>
       </c>
       <c r="E94">
-        <v>168.07</v>
+        <v>153007.526</v>
       </c>
       <c r="F94">
-        <v>1.211</v>
+        <v>2.655</v>
       </c>
       <c r="G94">
-        <v>0.226</v>
+        <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -2911,23 +2911,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_2 o más autos`</t>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
         </is>
       </c>
       <c r="C95">
-        <v>0.677</v>
+        <v>187.101</v>
       </c>
       <c r="D95">
-        <v>0.001</v>
+        <v>3</v>
       </c>
       <c r="E95">
-        <v>878.439</v>
+        <v>11668.338</v>
       </c>
       <c r="F95">
-        <v>-0.107</v>
+        <v>2.481</v>
       </c>
       <c r="G95">
-        <v>0.9149</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="96">
@@ -2938,23 +2938,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_1 motocicleta`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="C96">
-        <v>0.183</v>
+        <v>0.977</v>
       </c>
       <c r="D96">
-        <v>0.008</v>
+        <v>0.103</v>
       </c>
       <c r="E96">
-        <v>4.319</v>
+        <v>9.231</v>
       </c>
       <c r="F96">
-        <v>-1.052</v>
+        <v>-0.02</v>
       </c>
       <c r="G96">
-        <v>0.2927</v>
+        <v>0.9837</v>
       </c>
     </row>
     <row r="97">
@@ -2965,23 +2965,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_Sin motocicletas`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="C97">
-        <v>185338.858</v>
+        <v>0.008</v>
       </c>
       <c r="D97">
-        <v>780.525</v>
+        <v>0</v>
       </c>
       <c r="E97">
-        <v>44009464.078</v>
+        <v>3.536</v>
       </c>
       <c r="F97">
-        <v>4.346</v>
+        <v>-1.556</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>0.1196</v>
       </c>
     </row>
     <row r="98">
@@ -2992,23 +2992,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>`p22_Entre 11 y 15 km`</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="C98">
-        <v>5.533</v>
+        <v>0.099</v>
       </c>
       <c r="D98">
-        <v>0.028</v>
+        <v>0.023</v>
       </c>
       <c r="E98">
-        <v>1107.516</v>
+        <v>0.423</v>
       </c>
       <c r="F98">
-        <v>0.633</v>
+        <v>-3.126</v>
       </c>
       <c r="G98">
-        <v>0.5269</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="99">
@@ -3019,23 +3019,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>`p22_Entre 16 y 20 km`</t>
+          <t>p28_importancia_comodidad</t>
         </is>
       </c>
       <c r="C99">
-        <v>124.798</v>
+        <v>0.364</v>
       </c>
       <c r="D99">
-        <v>0.625</v>
+        <v>0.048</v>
       </c>
       <c r="E99">
-        <v>24935.561</v>
+        <v>2.766</v>
       </c>
       <c r="F99">
-        <v>1.786</v>
+        <v>-0.976</v>
       </c>
       <c r="G99">
-        <v>0.0741</v>
+        <v>0.3291</v>
       </c>
     </row>
     <row r="100">
@@ -3046,23 +3046,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>`p22_Entre 6 y 10 km`</t>
+          <t>p28_importancia_costo_compra</t>
         </is>
       </c>
       <c r="C100">
-        <v>197.674</v>
+        <v>3.87</v>
       </c>
       <c r="D100">
-        <v>1.01</v>
+        <v>1.247</v>
       </c>
       <c r="E100">
-        <v>38691.273</v>
+        <v>12.005</v>
       </c>
       <c r="F100">
-        <v>1.964</v>
+        <v>2.343</v>
       </c>
       <c r="G100">
-        <v>0.0496</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="101">
@@ -3073,23 +3073,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>`p22_Menos de 5 km`</t>
+          <t>p28_importancia_costo_uso</t>
         </is>
       </c>
       <c r="C101">
-        <v>2188.255</v>
+        <v>0.58</v>
       </c>
       <c r="D101">
-        <v>5.623</v>
+        <v>0.202</v>
       </c>
       <c r="E101">
-        <v>851534.6409999999</v>
+        <v>1.664</v>
       </c>
       <c r="F101">
-        <v>2.528</v>
+        <v>-1.013</v>
       </c>
       <c r="G101">
-        <v>0.0115</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="102">
@@ -3100,23 +3100,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>`p23_agregado_Compras y trámites`</t>
+          <t>p28_importancia_discriminacion</t>
         </is>
       </c>
       <c r="C102">
-        <v>0.049</v>
+        <v>0.335</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="E102">
-        <v>5.185</v>
+        <v>1.048</v>
       </c>
       <c r="F102">
-        <v>-1.267</v>
+        <v>-1.88</v>
       </c>
       <c r="G102">
-        <v>0.2052</v>
+        <v>0.0601</v>
       </c>
     </row>
     <row r="103">
@@ -3127,23 +3127,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>`p23_agregado_Cuidado y familia`</t>
+          <t>p28_importancia_emisiones</t>
         </is>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>6.143</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1.879</v>
       </c>
       <c r="E103">
-        <v>0.098</v>
+        <v>20.081</v>
       </c>
       <c r="F103">
-        <v>-2.491</v>
+        <v>3.004</v>
       </c>
       <c r="G103">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="104">
@@ -3154,23 +3154,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
+          <t>p28_importancia_riesgo_acoso</t>
         </is>
       </c>
       <c r="C104">
-        <v>6.954</v>
+        <v>0.646</v>
       </c>
       <c r="D104">
-        <v>0.037</v>
+        <v>0.215</v>
       </c>
       <c r="E104">
-        <v>1294.564</v>
+        <v>1.935</v>
       </c>
       <c r="F104">
-        <v>0.727</v>
+        <v>-0.781</v>
       </c>
       <c r="G104">
-        <v>0.4671</v>
+        <v>0.4347</v>
       </c>
     </row>
     <row r="105">
@@ -3181,23 +3181,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>`p23_agregado_Visitas sociales`</t>
+          <t>p28_importancia_riesgo_robo</t>
         </is>
       </c>
       <c r="C105">
-        <v>0.84</v>
+        <v>1.69</v>
       </c>
       <c r="D105">
-        <v>0.003</v>
+        <v>0.628</v>
       </c>
       <c r="E105">
-        <v>257.312</v>
+        <v>4.548</v>
       </c>
       <c r="F105">
-        <v>-0.06</v>
+        <v>1.04</v>
       </c>
       <c r="G105">
-        <v>0.9524</v>
+        <v>0.2985</v>
       </c>
     </row>
     <row r="106">
@@ -3208,23 +3208,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>p28_importancia_siniestralidad</t>
         </is>
       </c>
       <c r="C106">
-        <v>49.145</v>
+        <v>0.528</v>
       </c>
       <c r="D106">
-        <v>0.281</v>
+        <v>0.209</v>
       </c>
       <c r="E106">
-        <v>8603.823</v>
+        <v>1.337</v>
       </c>
       <c r="F106">
-        <v>1.478</v>
+        <v>-1.347</v>
       </c>
       <c r="G106">
-        <v>0.1394</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="107">
@@ -3235,23 +3235,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>p28_importancia_tiempo</t>
         </is>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>0.952</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>4.157</v>
       </c>
       <c r="F107">
-        <v>-4161238.649</v>
+        <v>-0.066</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>0.9475</v>
       </c>
     </row>
     <row r="108">
@@ -3262,23 +3262,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>p32_contaminacion_likert</t>
         </is>
       </c>
       <c r="C108">
-        <v>2.587</v>
+        <v>3.204</v>
       </c>
       <c r="D108">
-        <v>0.057</v>
+        <v>1.203</v>
       </c>
       <c r="E108">
-        <v>118.052</v>
+        <v>8.532999999999999</v>
       </c>
       <c r="F108">
-        <v>0.488</v>
+        <v>2.33</v>
       </c>
       <c r="G108">
-        <v>0.6259</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="109">
@@ -3289,23 +3289,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="C109">
-        <v>3.25</v>
+        <v>6.046</v>
       </c>
       <c r="D109">
-        <v>0.015</v>
+        <v>0.638</v>
       </c>
       <c r="E109">
-        <v>712.862</v>
+        <v>57.31</v>
       </c>
       <c r="F109">
-        <v>0.429</v>
+        <v>1.568</v>
       </c>
       <c r="G109">
-        <v>0.6682</v>
+        <v>0.1168</v>
       </c>
     </row>
     <row r="110">
@@ -3316,23 +3316,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="C110">
-        <v>5.204</v>
+        <v>9.092000000000001</v>
       </c>
       <c r="D110">
-        <v>0.035</v>
+        <v>0.163</v>
       </c>
       <c r="E110">
-        <v>765.698</v>
+        <v>507.638</v>
       </c>
       <c r="F110">
-        <v>0.648</v>
+        <v>1.076</v>
       </c>
       <c r="G110">
-        <v>0.5172</v>
+        <v>0.2821</v>
       </c>
     </row>
     <row r="111">
@@ -3343,23 +3343,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="C111">
-        <v>2256.569</v>
+        <v>30.571</v>
       </c>
       <c r="D111">
-        <v>4.736</v>
+        <v>2.819</v>
       </c>
       <c r="E111">
-        <v>1075273.87</v>
+        <v>331.544</v>
       </c>
       <c r="F111">
-        <v>2.454</v>
+        <v>2.812</v>
       </c>
       <c r="G111">
-        <v>0.0141</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="112">
@@ -3370,23 +3370,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="C112">
-        <v>1355.654</v>
+        <v>1194833.904</v>
       </c>
       <c r="D112">
-        <v>7.806</v>
+        <v>408.775</v>
       </c>
       <c r="E112">
-        <v>235443.517</v>
+        <v>3492455690.464</v>
       </c>
       <c r="F112">
-        <v>2.741</v>
+        <v>3.437</v>
       </c>
       <c r="G112">
-        <v>0.0061</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>p23_agregado_Estudio</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="C113">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>14.283</v>
+        <v>0.19</v>
       </c>
       <c r="F113">
-        <v>-1.193</v>
+        <v>-2.872</v>
       </c>
       <c r="G113">
-        <v>0.233</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="114">
@@ -3424,23 +3424,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="C114">
-        <v>0.051</v>
+        <v>0.068</v>
       </c>
       <c r="D114">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="E114">
-        <v>0.278</v>
+        <v>1.622</v>
       </c>
       <c r="F114">
-        <v>-3.446</v>
+        <v>-1.662</v>
       </c>
       <c r="G114">
-        <v>0.0005999999999999999</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -3451,509 +3451,509 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>p28_importancia_comodidad</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="C115">
-        <v>0.464</v>
+        <v>1.042</v>
       </c>
       <c r="D115">
-        <v>0.052</v>
+        <v>0.955</v>
       </c>
       <c r="E115">
-        <v>4.132</v>
+        <v>1.137</v>
       </c>
       <c r="F115">
-        <v>-0.6879999999999999</v>
+        <v>0.928</v>
       </c>
       <c r="G115">
-        <v>0.4913</v>
+        <v>0.3534</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_compra</t>
+          <t>(Intercept)</t>
         </is>
       </c>
       <c r="C116">
-        <v>4.731</v>
+        <v>0.008</v>
       </c>
       <c r="D116">
-        <v>1.278</v>
+        <v>0</v>
       </c>
       <c r="E116">
-        <v>17.513</v>
+        <v>118.776</v>
       </c>
       <c r="F116">
-        <v>2.328</v>
+        <v>-0.984</v>
       </c>
       <c r="G116">
-        <v>0.0199</v>
+        <v>0.3252</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>p28_importancia_costo_uso</t>
+          <t>`edad_r2_18 - 34 años`</t>
         </is>
       </c>
       <c r="C117">
-        <v>0.549</v>
+        <v>5.376</v>
       </c>
       <c r="D117">
-        <v>0.178</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E117">
-        <v>1.698</v>
+        <v>35.579</v>
       </c>
       <c r="F117">
-        <v>-1.04</v>
+        <v>1.744</v>
       </c>
       <c r="G117">
-        <v>0.2983</v>
+        <v>0.08110000000000001</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>p28_importancia_discriminacion</t>
+          <t>`edad_r2_55 - 80 años`</t>
         </is>
       </c>
       <c r="C118">
-        <v>0.285</v>
+        <v>6.671</v>
       </c>
       <c r="D118">
-        <v>0.075</v>
+        <v>0.389</v>
       </c>
       <c r="E118">
-        <v>1.078</v>
+        <v>114.418</v>
       </c>
       <c r="F118">
-        <v>-1.849</v>
+        <v>1.309</v>
       </c>
       <c r="G118">
-        <v>0.0644</v>
+        <v>0.1906</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>p28_importancia_emisiones</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="C119">
-        <v>6.784</v>
+        <v>1.397</v>
       </c>
       <c r="D119">
-        <v>1.865</v>
+        <v>0.052</v>
       </c>
       <c r="E119">
-        <v>24.681</v>
+        <v>37.879</v>
       </c>
       <c r="F119">
-        <v>2.906</v>
+        <v>0.199</v>
       </c>
       <c r="G119">
-        <v>0.0037</v>
+        <v>0.8425</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_acoso</t>
+          <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
       <c r="C120">
-        <v>0.734</v>
+        <v>0.555</v>
       </c>
       <c r="D120">
-        <v>0.221</v>
+        <v>0.06</v>
       </c>
       <c r="E120">
-        <v>2.432</v>
+        <v>5.174</v>
       </c>
       <c r="F120">
-        <v>-0.507</v>
+        <v>-0.517</v>
       </c>
       <c r="G120">
-        <v>0.6124000000000001</v>
+        <v>0.6051</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>p28_importancia_riesgo_robo</t>
+          <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
       <c r="C121">
-        <v>1.679</v>
+        <v>0.01</v>
       </c>
       <c r="D121">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>5.142</v>
+        <v>10.093</v>
       </c>
       <c r="F121">
-        <v>0.907</v>
+        <v>-1.302</v>
       </c>
       <c r="G121">
-        <v>0.3643</v>
+        <v>0.1929</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>p28_importancia_siniestralidad</t>
+          <t>`p16_motos_agregado_1 motocicleta`</t>
         </is>
       </c>
       <c r="C122">
-        <v>0.466</v>
+        <v>0.118</v>
       </c>
       <c r="D122">
-        <v>0.17</v>
+        <v>0.013</v>
       </c>
       <c r="E122">
-        <v>1.277</v>
+        <v>1.093</v>
       </c>
       <c r="F122">
-        <v>-1.485</v>
+        <v>-1.882</v>
       </c>
       <c r="G122">
-        <v>0.1376</v>
+        <v>0.0599</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>p28_importancia_tiempo</t>
+          <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
       <c r="C123">
-        <v>0.626</v>
+        <v>10228.582</v>
       </c>
       <c r="D123">
-        <v>0.144</v>
+        <v>127.879</v>
       </c>
       <c r="E123">
-        <v>2.724</v>
+        <v>818145.4889999999</v>
       </c>
       <c r="F123">
-        <v>-0.625</v>
+        <v>4.13</v>
       </c>
       <c r="G123">
-        <v>0.5321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>p32_contaminacion_likert</t>
+          <t>`p22_Entre 11 y 15 km`</t>
         </is>
       </c>
       <c r="C124">
-        <v>3.598</v>
+        <v>1.262</v>
       </c>
       <c r="D124">
-        <v>1.205</v>
+        <v>0.035</v>
       </c>
       <c r="E124">
-        <v>10.745</v>
+        <v>45.083</v>
       </c>
       <c r="F124">
-        <v>2.294</v>
+        <v>0.128</v>
       </c>
       <c r="G124">
-        <v>0.0218</v>
+        <v>0.8985</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>p36_influencia_amigos</t>
+          <t>`p22_Entre 16 y 20 km`</t>
         </is>
       </c>
       <c r="C125">
-        <v>1.674</v>
+        <v>19.006</v>
       </c>
       <c r="D125">
-        <v>0.45</v>
+        <v>0.369</v>
       </c>
       <c r="E125">
-        <v>6.235</v>
+        <v>979.032</v>
       </c>
       <c r="F125">
-        <v>0.768</v>
+        <v>1.464</v>
       </c>
       <c r="G125">
-        <v>0.4424</v>
+        <v>0.1431</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>p37_influencia_familia</t>
+          <t>`p22_Entre 6 y 10 km`</t>
         </is>
       </c>
       <c r="C126">
-        <v>0.585</v>
+        <v>52.229</v>
       </c>
       <c r="D126">
-        <v>0.178</v>
+        <v>1.393</v>
       </c>
       <c r="E126">
-        <v>1.92</v>
+        <v>1957.822</v>
       </c>
       <c r="F126">
-        <v>-0.884</v>
+        <v>2.139</v>
       </c>
       <c r="G126">
-        <v>0.3767</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>p38p38_dummy_1</t>
+          <t>`p22_Menos de 5 km`</t>
         </is>
       </c>
       <c r="C127">
-        <v>12.308</v>
+        <v>502.784</v>
       </c>
       <c r="D127">
-        <v>0.802</v>
+        <v>7.137</v>
       </c>
       <c r="E127">
-        <v>188.866</v>
+        <v>35418.369</v>
       </c>
       <c r="F127">
-        <v>1.802</v>
+        <v>2.865</v>
       </c>
       <c r="G127">
-        <v>0.0716</v>
+        <v>0.0042</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>p40_Mujer</t>
+          <t>`p23_agregado_Compras y trámites`</t>
         </is>
       </c>
       <c r="C128">
-        <v>42.388</v>
+        <v>0.219</v>
       </c>
       <c r="D128">
-        <v>2.713</v>
+        <v>0.005</v>
       </c>
       <c r="E128">
-        <v>662.239</v>
+        <v>8.920999999999999</v>
       </c>
       <c r="F128">
-        <v>2.672</v>
+        <v>-0.803</v>
       </c>
       <c r="G128">
-        <v>0.0075</v>
+        <v>0.4219</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>p5_agregado_Secundaria</t>
+          <t>`p23_agregado_Cuidado y familia`</t>
         </is>
       </c>
       <c r="C129">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="E129">
-        <v>401.787</v>
+        <v>0.157</v>
       </c>
       <c r="F129">
-        <v>0.621</v>
+        <v>-2.534</v>
       </c>
       <c r="G129">
-        <v>0.5348000000000001</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>p7_agregado_Estudiante</t>
+          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
         </is>
       </c>
       <c r="C130">
-        <v>1240635.76</v>
+        <v>6.259</v>
       </c>
       <c r="D130">
-        <v>124.363</v>
+        <v>0.267</v>
       </c>
       <c r="E130">
-        <v>12376481142.429</v>
+        <v>146.772</v>
       </c>
       <c r="F130">
-        <v>2.987</v>
+        <v>1.139</v>
       </c>
       <c r="G130">
-        <v>0.0028</v>
+        <v>0.2546</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>p9_estrato3_Bajo</t>
+          <t>`p23_agregado_Visitas sociales`</t>
         </is>
       </c>
       <c r="C131">
+        <v>0.078</v>
+      </c>
+      <c r="D131">
         <v>0.001</v>
       </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
       <c r="E131">
-        <v>0.08799999999999999</v>
+        <v>10.621</v>
       </c>
       <c r="F131">
-        <v>-2.96</v>
+        <v>-1.018</v>
       </c>
       <c r="G131">
-        <v>0.0031</v>
+        <v>0.3088</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>p9_estrato3_Medio</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="C132">
-        <v>0.013</v>
+        <v>621.638</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>4.437</v>
       </c>
       <c r="E132">
-        <v>0.772</v>
+        <v>87092.962</v>
       </c>
       <c r="F132">
-        <v>-2.083</v>
+        <v>2.551</v>
       </c>
       <c r="G132">
-        <v>0.0372</v>
+        <v>0.0107</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Taxi / Plataforma</t>
+          <t>Transporte público</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>tiempo_total</t>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
         </is>
       </c>
       <c r="C133">
-        <v>1.057</v>
+        <v>108.969</v>
       </c>
       <c r="D133">
-        <v>0.946</v>
+        <v>2.156</v>
       </c>
       <c r="E133">
-        <v>1.182</v>
+        <v>5506.583</v>
       </c>
       <c r="F133">
-        <v>0.982</v>
+        <v>2.344</v>
       </c>
       <c r="G133">
-        <v>0.326</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="134">
@@ -3964,23 +3964,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>(Intercept)</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="C134">
-        <v>0.1</v>
+        <v>0.482</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E134">
-        <v>3789.062</v>
+        <v>3.37</v>
       </c>
       <c r="F134">
-        <v>-0.428</v>
+        <v>-0.736</v>
       </c>
       <c r="G134">
-        <v>0.6689000000000001</v>
+        <v>0.4616</v>
       </c>
     </row>
     <row r="135">
@@ -3991,23 +3991,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>`edad_r2_18 - 34 años`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="C135">
-        <v>9.443</v>
+        <v>0.168</v>
       </c>
       <c r="D135">
-        <v>0.85</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E135">
-        <v>104.919</v>
+        <v>3.263</v>
       </c>
       <c r="F135">
-        <v>1.828</v>
+        <v>-1.178</v>
       </c>
       <c r="G135">
-        <v>0.06759999999999999</v>
+        <v>0.2388</v>
       </c>
     </row>
     <row r="136">
@@ -4018,23 +4018,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>`edad_r2_55 - 80 años`</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="C136">
-        <v>17.458</v>
+        <v>0.14</v>
       </c>
       <c r="D136">
-        <v>0.397</v>
+        <v>0.035</v>
       </c>
       <c r="E136">
-        <v>767.9930000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="F136">
-        <v>1.481</v>
+        <v>-2.756</v>
       </c>
       <c r="G136">
-        <v>0.1385</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="137">
@@ -4045,23 +4045,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>p28_importancia_comodidad</t>
         </is>
       </c>
       <c r="C137">
-        <v>7.183</v>
+        <v>0.242</v>
       </c>
       <c r="D137">
-        <v>0.115</v>
+        <v>0.033</v>
       </c>
       <c r="E137">
-        <v>449.465</v>
+        <v>1.753</v>
       </c>
       <c r="F137">
-        <v>0.9340000000000001</v>
+        <v>-1.405</v>
       </c>
       <c r="G137">
-        <v>0.3502</v>
+        <v>0.1601</v>
       </c>
     </row>
     <row r="138">
@@ -4072,23 +4072,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_1 auto`</t>
+          <t>p28_importancia_costo_compra</t>
         </is>
       </c>
       <c r="C138">
-        <v>0.436</v>
+        <v>4.348</v>
       </c>
       <c r="D138">
-        <v>0.026</v>
+        <v>1.542</v>
       </c>
       <c r="E138">
-        <v>7.22</v>
+        <v>12.26</v>
       </c>
       <c r="F138">
-        <v>-0.579</v>
+        <v>2.779</v>
       </c>
       <c r="G138">
-        <v>0.5624</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="139">
@@ -4099,23 +4099,23 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_2 o más autos`</t>
+          <t>p28_importancia_costo_uso</t>
         </is>
       </c>
       <c r="C139">
-        <v>0.007</v>
+        <v>0.374</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="E139">
-        <v>16.144</v>
+        <v>0.96</v>
       </c>
       <c r="F139">
-        <v>-1.261</v>
+        <v>-2.046</v>
       </c>
       <c r="G139">
-        <v>0.2074</v>
+        <v>0.0408</v>
       </c>
     </row>
     <row r="140">
@@ -4126,23 +4126,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_1 motocicleta`</t>
+          <t>p28_importancia_discriminacion</t>
         </is>
       </c>
       <c r="C140">
-        <v>0.08400000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="D140">
-        <v>0.006</v>
+        <v>0.137</v>
       </c>
       <c r="E140">
-        <v>1.107</v>
+        <v>1.172</v>
       </c>
       <c r="F140">
-        <v>-1.883</v>
+        <v>-1.671</v>
       </c>
       <c r="G140">
-        <v>0.0598</v>
+        <v>0.0948</v>
       </c>
     </row>
     <row r="141">
@@ -4153,23 +4153,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_Sin motocicletas`</t>
+          <t>p28_importancia_emisiones</t>
         </is>
       </c>
       <c r="C141">
-        <v>27597.558</v>
+        <v>5.475</v>
       </c>
       <c r="D141">
-        <v>169.924</v>
+        <v>1.948</v>
       </c>
       <c r="E141">
-        <v>4482159.934</v>
+        <v>15.39</v>
       </c>
       <c r="F141">
-        <v>3.937</v>
+        <v>3.224</v>
       </c>
       <c r="G141">
-        <v>0.0001</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="142">
@@ -4180,23 +4180,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>`p22_Entre 11 y 15 km`</t>
+          <t>p28_importancia_riesgo_acoso</t>
         </is>
       </c>
       <c r="C142">
-        <v>3.706</v>
+        <v>1.122</v>
       </c>
       <c r="D142">
-        <v>0.039</v>
+        <v>0.401</v>
       </c>
       <c r="E142">
-        <v>353.107</v>
+        <v>3.135</v>
       </c>
       <c r="F142">
-        <v>0.5629999999999999</v>
+        <v>0.219</v>
       </c>
       <c r="G142">
-        <v>0.5731000000000001</v>
+        <v>0.8269</v>
       </c>
     </row>
     <row r="143">
@@ -4207,23 +4207,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>`p22_Entre 16 y 20 km`</t>
+          <t>p28_importancia_riesgo_robo</t>
         </is>
       </c>
       <c r="C143">
-        <v>50.646</v>
+        <v>0.844</v>
       </c>
       <c r="D143">
-        <v>0.409</v>
+        <v>0.359</v>
       </c>
       <c r="E143">
-        <v>6264.814</v>
+        <v>1.982</v>
       </c>
       <c r="F143">
-        <v>1.597</v>
+        <v>-0.39</v>
       </c>
       <c r="G143">
-        <v>0.1103</v>
+        <v>0.6969</v>
       </c>
     </row>
     <row r="144">
@@ -4234,23 +4234,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>`p22_Entre 6 y 10 km`</t>
+          <t>p28_importancia_siniestralidad</t>
         </is>
       </c>
       <c r="C144">
-        <v>289.81</v>
+        <v>0.51</v>
       </c>
       <c r="D144">
-        <v>2.669</v>
+        <v>0.246</v>
       </c>
       <c r="E144">
-        <v>31473.786</v>
+        <v>1.06</v>
       </c>
       <c r="F144">
-        <v>2.37</v>
+        <v>-1.804</v>
       </c>
       <c r="G144">
-        <v>0.0178</v>
+        <v>0.0712</v>
       </c>
     </row>
     <row r="145">
@@ -4261,23 +4261,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>`p22_Menos de 5 km`</t>
+          <t>p28_importancia_tiempo</t>
         </is>
       </c>
       <c r="C145">
-        <v>3817.629</v>
+        <v>1.753</v>
       </c>
       <c r="D145">
-        <v>16.388</v>
+        <v>0.461</v>
       </c>
       <c r="E145">
-        <v>889315.596</v>
+        <v>6.66</v>
       </c>
       <c r="F145">
-        <v>2.966</v>
+        <v>0.824</v>
       </c>
       <c r="G145">
-        <v>0.003</v>
+        <v>0.4098</v>
       </c>
     </row>
     <row r="146">
@@ -4288,23 +4288,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>`p23_agregado_Compras y trámites`</t>
+          <t>p32_contaminacion_likert</t>
         </is>
       </c>
       <c r="C146">
-        <v>0.106</v>
+        <v>1.198</v>
       </c>
       <c r="D146">
-        <v>0.002</v>
+        <v>0.508</v>
       </c>
       <c r="E146">
-        <v>7.321</v>
+        <v>2.829</v>
       </c>
       <c r="F146">
-        <v>-1.039</v>
+        <v>0.413</v>
       </c>
       <c r="G146">
-        <v>0.2989</v>
+        <v>0.6798</v>
       </c>
     </row>
     <row r="147">
@@ -4315,23 +4315,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>`p23_agregado_Cuidado y familia`</t>
+          <t>p38p38_dummy_1</t>
         </is>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>3.663</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="E147">
-        <v>0.107</v>
+        <v>26.676</v>
       </c>
       <c r="F147">
-        <v>-2.501</v>
+        <v>1.281</v>
       </c>
       <c r="G147">
-        <v>0.0124</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="148">
@@ -4342,23 +4342,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="C148">
-        <v>5.604</v>
+        <v>8.06</v>
       </c>
       <c r="D148">
-        <v>0.034</v>
+        <v>0.158</v>
       </c>
       <c r="E148">
-        <v>914.952</v>
+        <v>411.991</v>
       </c>
       <c r="F148">
-        <v>0.663</v>
+        <v>1.04</v>
       </c>
       <c r="G148">
-        <v>0.5073</v>
+        <v>0.2985</v>
       </c>
     </row>
     <row r="149">
@@ -4369,23 +4369,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>`p23_agregado_Visitas sociales`</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="C149">
-        <v>0.121</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>1.126</v>
       </c>
       <c r="E149">
-        <v>41.81</v>
+        <v>60.203</v>
       </c>
       <c r="F149">
-        <v>-0.708</v>
+        <v>2.077</v>
       </c>
       <c r="G149">
-        <v>0.479</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="150">
@@ -4396,23 +4396,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="C150">
-        <v>33.796</v>
+        <v>52995.731</v>
       </c>
       <c r="D150">
-        <v>0.182</v>
+        <v>136.527</v>
       </c>
       <c r="E150">
-        <v>6267.97</v>
+        <v>20571315.246</v>
       </c>
       <c r="F150">
-        <v>1.321</v>
+        <v>3.576</v>
       </c>
       <c r="G150">
-        <v>0.1865</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="151">
@@ -4423,23 +4423,23 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="C151">
-        <v>27.663</v>
+        <v>0.223</v>
       </c>
       <c r="D151">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E151">
-        <v>665130.6090000001</v>
+        <v>5.253</v>
       </c>
       <c r="F151">
-        <v>0.645</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="G151">
-        <v>0.5189</v>
+        <v>0.3515</v>
       </c>
     </row>
     <row r="152">
@@ -4450,23 +4450,23 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="C152">
-        <v>1.246</v>
+        <v>2.73</v>
       </c>
       <c r="D152">
-        <v>0.041</v>
+        <v>0.146</v>
       </c>
       <c r="E152">
-        <v>37.942</v>
+        <v>51.09</v>
       </c>
       <c r="F152">
-        <v>0.126</v>
+        <v>0.672</v>
       </c>
       <c r="G152">
-        <v>0.8994</v>
+        <v>0.5014999999999999</v>
       </c>
     </row>
     <row r="153">
@@ -4477,670 +4477,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="C153">
-        <v>0.06900000000000001</v>
+        <v>1.226</v>
       </c>
       <c r="D153">
-        <v>0.001</v>
+        <v>1.13</v>
       </c>
       <c r="E153">
-        <v>4.427</v>
+        <v>1.33</v>
       </c>
       <c r="F153">
-        <v>-1.258</v>
+        <v>4.908</v>
       </c>
       <c r="G153">
-        <v>0.2083</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
-        </is>
-      </c>
-      <c r="C154">
-        <v>0.082</v>
-      </c>
-      <c r="D154">
-        <v>0.002</v>
-      </c>
-      <c r="E154">
-        <v>3.319</v>
-      </c>
-      <c r="F154">
-        <v>-1.324</v>
-      </c>
-      <c r="G154">
-        <v>0.1854</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
-        </is>
-      </c>
-      <c r="C155">
-        <v>2792.597</v>
-      </c>
-      <c r="D155">
-        <v>5.777</v>
-      </c>
-      <c r="E155">
-        <v>1349904.862</v>
-      </c>
-      <c r="F155">
-        <v>2.516</v>
-      </c>
-      <c r="G155">
-        <v>0.0119</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
-        </is>
-      </c>
-      <c r="C156">
-        <v>939.22</v>
-      </c>
-      <c r="D156">
-        <v>6.654</v>
-      </c>
-      <c r="E156">
-        <v>132569.023</v>
-      </c>
-      <c r="F156">
-        <v>2.71</v>
-      </c>
-      <c r="G156">
-        <v>0.0067</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>p23_agregado_Estudio</t>
-        </is>
-      </c>
-      <c r="C157">
-        <v>0.156</v>
-      </c>
-      <c r="D157">
-        <v>0.006</v>
-      </c>
-      <c r="E157">
-        <v>3.837</v>
-      </c>
-      <c r="F157">
-        <v>-1.137</v>
-      </c>
-      <c r="G157">
-        <v>0.2556</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>p24</t>
-        </is>
-      </c>
-      <c r="C158">
-        <v>0.104</v>
-      </c>
-      <c r="D158">
-        <v>0.021</v>
-      </c>
-      <c r="E158">
-        <v>0.514</v>
-      </c>
-      <c r="F158">
-        <v>-2.773</v>
-      </c>
-      <c r="G158">
-        <v>0.0056</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>p28_importancia_comodidad</t>
-        </is>
-      </c>
-      <c r="C159">
-        <v>0.297</v>
-      </c>
-      <c r="D159">
-        <v>0.035</v>
-      </c>
-      <c r="E159">
-        <v>2.49</v>
-      </c>
-      <c r="F159">
-        <v>-1.119</v>
-      </c>
-      <c r="G159">
-        <v>0.2631</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>p28_importancia_costo_compra</t>
-        </is>
-      </c>
-      <c r="C160">
-        <v>4.764</v>
-      </c>
-      <c r="D160">
-        <v>1.452</v>
-      </c>
-      <c r="E160">
-        <v>15.631</v>
-      </c>
-      <c r="F160">
-        <v>2.575</v>
-      </c>
-      <c r="G160">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>p28_importancia_costo_uso</t>
-        </is>
-      </c>
-      <c r="C161">
-        <v>0.373</v>
-      </c>
-      <c r="D161">
-        <v>0.132</v>
-      </c>
-      <c r="E161">
-        <v>1.06</v>
-      </c>
-      <c r="F161">
-        <v>-1.851</v>
-      </c>
-      <c r="G161">
-        <v>0.0641</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>p28_importancia_discriminacion</t>
-        </is>
-      </c>
-      <c r="C162">
-        <v>0.288</v>
-      </c>
-      <c r="D162">
-        <v>0.081</v>
-      </c>
-      <c r="E162">
-        <v>1.02</v>
-      </c>
-      <c r="F162">
-        <v>-1.929</v>
-      </c>
-      <c r="G162">
-        <v>0.0538</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>p28_importancia_emisiones</t>
-        </is>
-      </c>
-      <c r="C163">
-        <v>6.008</v>
-      </c>
-      <c r="D163">
-        <v>1.95</v>
-      </c>
-      <c r="E163">
-        <v>18.512</v>
-      </c>
-      <c r="F163">
-        <v>3.123</v>
-      </c>
-      <c r="G163">
-        <v>0.0018</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>p28_importancia_riesgo_acoso</t>
-        </is>
-      </c>
-      <c r="C164">
-        <v>1.499</v>
-      </c>
-      <c r="D164">
-        <v>0.492</v>
-      </c>
-      <c r="E164">
-        <v>4.565</v>
-      </c>
-      <c r="F164">
-        <v>0.713</v>
-      </c>
-      <c r="G164">
-        <v>0.4758</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>p28_importancia_riesgo_robo</t>
-        </is>
-      </c>
-      <c r="C165">
-        <v>0.737</v>
-      </c>
-      <c r="D165">
-        <v>0.278</v>
-      </c>
-      <c r="E165">
-        <v>1.951</v>
-      </c>
-      <c r="F165">
-        <v>-0.615</v>
-      </c>
-      <c r="G165">
-        <v>0.5383</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>p28_importancia_siniestralidad</t>
-        </is>
-      </c>
-      <c r="C166">
-        <v>0.423</v>
-      </c>
-      <c r="D166">
-        <v>0.194</v>
-      </c>
-      <c r="E166">
-        <v>0.924</v>
-      </c>
-      <c r="F166">
-        <v>-2.159</v>
-      </c>
-      <c r="G166">
-        <v>0.0308</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>p28_importancia_tiempo</t>
-        </is>
-      </c>
-      <c r="C167">
-        <v>1.212</v>
-      </c>
-      <c r="D167">
-        <v>0.345</v>
-      </c>
-      <c r="E167">
-        <v>4.256</v>
-      </c>
-      <c r="F167">
-        <v>0.3</v>
-      </c>
-      <c r="G167">
-        <v>0.7643</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>p32_contaminacion_likert</t>
-        </is>
-      </c>
-      <c r="C168">
-        <v>1.324</v>
-      </c>
-      <c r="D168">
-        <v>0.509</v>
-      </c>
-      <c r="E168">
-        <v>3.448</v>
-      </c>
-      <c r="F168">
-        <v>0.576</v>
-      </c>
-      <c r="G168">
-        <v>0.5649</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>p36_influencia_amigos</t>
-        </is>
-      </c>
-      <c r="C169">
-        <v>1.75</v>
-      </c>
-      <c r="D169">
-        <v>0.514</v>
-      </c>
-      <c r="E169">
-        <v>5.959</v>
-      </c>
-      <c r="F169">
-        <v>0.895</v>
-      </c>
-      <c r="G169">
-        <v>0.3709</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>p37_influencia_familia</t>
-        </is>
-      </c>
-      <c r="C170">
-        <v>0.432</v>
-      </c>
-      <c r="D170">
-        <v>0.141</v>
-      </c>
-      <c r="E170">
-        <v>1.323</v>
-      </c>
-      <c r="F170">
-        <v>-1.469</v>
-      </c>
-      <c r="G170">
-        <v>0.1419</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>p38p38_dummy_1</t>
-        </is>
-      </c>
-      <c r="C171">
-        <v>4.813</v>
-      </c>
-      <c r="D171">
-        <v>0.442</v>
-      </c>
-      <c r="E171">
-        <v>52.383</v>
-      </c>
-      <c r="F171">
-        <v>1.29</v>
-      </c>
-      <c r="G171">
-        <v>0.197</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>p40_Mujer</t>
-        </is>
-      </c>
-      <c r="C172">
-        <v>13.158</v>
-      </c>
-      <c r="D172">
-        <v>1.285</v>
-      </c>
-      <c r="E172">
-        <v>134.713</v>
-      </c>
-      <c r="F172">
-        <v>2.171</v>
-      </c>
-      <c r="G172">
-        <v>0.0299</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>p5_agregado_Secundaria</t>
-        </is>
-      </c>
-      <c r="C173">
-        <v>0.077</v>
-      </c>
-      <c r="D173">
-        <v>0.003</v>
-      </c>
-      <c r="E173">
-        <v>1.811</v>
-      </c>
-      <c r="F173">
-        <v>-1.591</v>
-      </c>
-      <c r="G173">
-        <v>0.1116</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>p7_agregado_Estudiante</t>
-        </is>
-      </c>
-      <c r="C174">
-        <v>91326.143</v>
-      </c>
-      <c r="D174">
-        <v>108.053</v>
-      </c>
-      <c r="E174">
-        <v>77188495.934</v>
-      </c>
-      <c r="F174">
-        <v>3.322</v>
-      </c>
-      <c r="G174">
-        <v>0.0009</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>p9_estrato3_Bajo</t>
-        </is>
-      </c>
-      <c r="C175">
-        <v>0.045</v>
-      </c>
-      <c r="D175">
-        <v>0.001</v>
-      </c>
-      <c r="E175">
-        <v>3.33</v>
-      </c>
-      <c r="F175">
-        <v>-1.411</v>
-      </c>
-      <c r="G175">
-        <v>0.1583</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>p9_estrato3_Medio</t>
-        </is>
-      </c>
-      <c r="C176">
-        <v>0.873</v>
-      </c>
-      <c r="D176">
-        <v>0.022</v>
-      </c>
-      <c r="E176">
-        <v>34.285</v>
-      </c>
-      <c r="F176">
-        <v>-0.073</v>
-      </c>
-      <c r="G176">
-        <v>0.9422</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Transporte público</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>tiempo_total</t>
-        </is>
-      </c>
-      <c r="C177">
-        <v>1.261</v>
-      </c>
-      <c r="D177">
-        <v>1.138</v>
-      </c>
-      <c r="E177">
-        <v>1.397</v>
-      </c>
-      <c r="F177">
-        <v>4.436</v>
-      </c>
-      <c r="G177">
         <v>0</v>
       </c>
     </row>
@@ -5151,7 +4503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AR5"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5217,160 +4569,130 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>p36_influencia_amigos</t>
+          <t>tiempo_total</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>p37_influencia_familia</t>
+          <t>`edad_r2_18 - 34 años`</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>tiempo_total</t>
+          <t>`edad_r2_55 - 80 años`</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>`edad_r2_18 - 34 años`</t>
+          <t>p3_minoria_Sí</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>`edad_r2_55 - 80 años`</t>
+          <t>educacion_Secundaria</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>`p3_agregado_Población afrodescendiente`</t>
+          <t>`educacion_Primaria o menos`</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>`p3_agregado_Sin respuesta`</t>
+          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>`p3_agregado_Pueblos indígenas`</t>
+          <t>`p7_agregado_Desocupado o inactivo`</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>p5_agregado_Secundaria</t>
+          <t>p7_agregado_Estudiante</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>`p5_agregado_Primaria o menos`</t>
+          <t>p9_estrato3_Medio</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>`p5_agregado_Técnico / Tecnológico`</t>
+          <t>p9_estrato3_Bajo</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>`p7_agregado_Trabajo doméstico no remunerado`</t>
+          <t>p40_Mujer</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>`p7_agregado_Desocupado o inactivo`</t>
+          <t>`p15_autos_agregado_1 auto`</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>p7_agregado_Estudiante</t>
+          <t>`p15_autos_agregado_2 o más autos`</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>p9_estrato3_Medio</t>
+          <t>`p16_motos_agregado_Sin motocicletas`</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>p9_estrato3_Bajo</t>
+          <t>`p16_motos_agregado_1 motocicleta`</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>`p12_dificultad_binaria_Con alguna dificultad`</t>
+          <t>`p22_Entre 16 y 20 km`</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>p40_Mujer</t>
+          <t>`p22_Entre 11 y 15 km`</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_1 auto`</t>
+          <t>`p22_Entre 6 y 10 km`</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>`p15_autos_agregado_2 o más autos`</t>
+          <t>`p22_Menos de 5 km`</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_Sin motocicletas`</t>
+          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>`p16_motos_agregado_1 motocicleta`</t>
+          <t>`p23_agregado_Compras y trámites`</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>`p22_Entre 16 y 20 km`</t>
+          <t>p23_agregado_Estudio</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>`p22_Entre 11 y 15 km`</t>
+          <t>`p23_agregado_Visitas sociales`</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>`p22_Entre 6 y 10 km`</t>
+          <t>`p23_agregado_Cuidado y familia`</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>`p22_Menos de 5 km`</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>`p23_agregado_Recreación, salud y actividades personales`</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>`p23_agregado_Compras y trámites`</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>p23_agregado_Estudio</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>`p23_agregado_Visitas sociales`</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>`p23_agregado_Cuidado y familia`</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>p38p38_dummy_1</t>
         </is>
@@ -5381,133 +4703,115 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>1.561</v>
+        <v>2.455</v>
       </c>
       <c r="C2">
-        <v>5.268</v>
+        <v>3.151</v>
       </c>
       <c r="D2">
-        <v>0.307</v>
+        <v>0.157</v>
       </c>
       <c r="E2">
-        <v>0.439</v>
+        <v>1.257</v>
       </c>
       <c r="F2">
-        <v>1.929</v>
+        <v>1.485</v>
       </c>
       <c r="G2">
-        <v>23.194</v>
+        <v>42.15</v>
       </c>
       <c r="H2">
-        <v>0.294</v>
+        <v>0.15</v>
       </c>
       <c r="I2">
-        <v>0.285</v>
+        <v>0.367</v>
       </c>
       <c r="J2">
-        <v>11.35</v>
+        <v>7.763</v>
       </c>
       <c r="K2">
+        <v>0.102</v>
+      </c>
+      <c r="L2">
+        <v>77.504</v>
+      </c>
+      <c r="M2">
+        <v>1.009</v>
+      </c>
+      <c r="N2">
+        <v>7.282</v>
+      </c>
+      <c r="O2">
+        <v>74.005</v>
+      </c>
+      <c r="P2">
+        <v>0.74</v>
+      </c>
+      <c r="Q2">
+        <v>113.656</v>
+      </c>
+      <c r="R2">
+        <v>30113.717</v>
+      </c>
+      <c r="S2">
+        <v>261.277</v>
+      </c>
+      <c r="T2">
+        <v>5393.784</v>
+      </c>
+      <c r="U2">
+        <v>70303.44100000001</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>73.678</v>
+      </c>
+      <c r="Y2">
+        <v>318117361.629</v>
+      </c>
+      <c r="Z2">
+        <v>32282181154.437</v>
+      </c>
+      <c r="AA2">
+        <v>238175166.88</v>
+      </c>
+      <c r="AB2">
+        <v>7.888</v>
+      </c>
+      <c r="AC2">
+        <v>0.183</v>
+      </c>
+      <c r="AD2">
+        <v>12.961</v>
+      </c>
+      <c r="AE2">
+        <v>135.965</v>
+      </c>
+      <c r="AF2">
+        <v>0.03</v>
+      </c>
+      <c r="AG2">
+        <v>0.006</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
         <v>0.042</v>
       </c>
-      <c r="L2">
-        <v>17.387</v>
-      </c>
-      <c r="M2">
-        <v>4.864</v>
-      </c>
-      <c r="N2">
-        <v>0.109</v>
-      </c>
-      <c r="O2">
-        <v>1.051</v>
-      </c>
-      <c r="P2">
-        <v>4.712</v>
-      </c>
-      <c r="Q2">
-        <v>87.25</v>
-      </c>
-      <c r="R2">
-        <v>2.127</v>
-      </c>
-      <c r="S2">
-        <v>229.963</v>
-      </c>
-      <c r="T2">
-        <v>702475.066</v>
-      </c>
-      <c r="U2">
-        <v>39.799</v>
-      </c>
-      <c r="V2">
-        <v>12813.462</v>
-      </c>
-      <c r="W2">
-        <v>0.08</v>
-      </c>
-      <c r="X2">
-        <v>1545.852</v>
-      </c>
-      <c r="Y2">
-        <v>3798.043</v>
-      </c>
-      <c r="Z2">
-        <v>2459301.266</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0.066</v>
-      </c>
-      <c r="AD2">
-        <v>82.251</v>
-      </c>
-      <c r="AE2">
-        <v>31733508.72</v>
-      </c>
-      <c r="AF2">
-        <v>317674076145.61</v>
-      </c>
-      <c r="AG2">
-        <v>1631250710.574</v>
-      </c>
-      <c r="AH2">
-        <v>21.323</v>
-      </c>
-      <c r="AI2">
-        <v>0.404</v>
-      </c>
-      <c r="AJ2">
-        <v>1939.383</v>
-      </c>
       <c r="AK2">
-        <v>9333.611000000001</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>23.409</v>
-      </c>
-      <c r="AM2">
-        <v>0.003</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0.594</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>118.479</v>
+        <v>16.762</v>
       </c>
     </row>
     <row r="3">
@@ -5515,401 +4819,347 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>0.065</v>
+        <v>0.108</v>
       </c>
       <c r="C3">
-        <v>11.099</v>
+        <v>6.48</v>
       </c>
       <c r="D3">
-        <v>0.51</v>
+        <v>0.529</v>
       </c>
       <c r="E3">
-        <v>0.07199999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="F3">
-        <v>0.705</v>
+        <v>1.201</v>
       </c>
       <c r="G3">
-        <v>2.126</v>
+        <v>1.588</v>
       </c>
       <c r="H3">
-        <v>1.553</v>
+        <v>1.044</v>
       </c>
       <c r="I3">
-        <v>0.173</v>
+        <v>0.367</v>
       </c>
       <c r="J3">
-        <v>7.165</v>
+        <v>5.337</v>
       </c>
       <c r="K3">
-        <v>0.282</v>
+        <v>0.446</v>
       </c>
       <c r="L3">
-        <v>0.08500000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="M3">
-        <v>1.044</v>
+        <v>1.175</v>
       </c>
       <c r="N3">
-        <v>1.791</v>
+        <v>1.573</v>
       </c>
       <c r="O3">
-        <v>1.197</v>
+        <v>350.639</v>
       </c>
       <c r="P3">
-        <v>0.43</v>
+        <v>10.011</v>
       </c>
       <c r="Q3">
-        <v>2399.345</v>
+        <v>10.31</v>
       </c>
       <c r="R3">
-        <v>31.968</v>
+        <v>1192.181</v>
       </c>
       <c r="S3">
-        <v>1.752</v>
+        <v>0.366</v>
       </c>
       <c r="T3">
-        <v>111.347</v>
+        <v>0.701</v>
       </c>
       <c r="U3">
-        <v>1266.953</v>
+        <v>131028.679</v>
       </c>
       <c r="V3">
-        <v>47041.96</v>
+        <v>0.019</v>
       </c>
       <c r="W3">
-        <v>12.632</v>
+        <v>0.003</v>
       </c>
       <c r="X3">
-        <v>19.246</v>
+        <v>0.659</v>
       </c>
       <c r="Y3">
-        <v>0.124</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="Z3">
-        <v>147113.85</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.002</v>
+        <v>8789783249.187</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>813295.889</v>
       </c>
       <c r="AC3">
-        <v>17.087</v>
+        <v>15652783.701</v>
       </c>
       <c r="AD3">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>93.777</v>
+        <v>642543.096</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>126296438.385</v>
       </c>
       <c r="AG3">
-        <v>6358846200.771</v>
+        <v>3.953</v>
       </c>
       <c r="AH3">
-        <v>374763.834</v>
+        <v>0.329</v>
       </c>
       <c r="AI3">
-        <v>165987.919</v>
+        <v>0.113</v>
       </c>
       <c r="AJ3">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>4086.136</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1567532.147</v>
-      </c>
-      <c r="AM3">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AN3">
-        <v>0.076</v>
-      </c>
-      <c r="AO3">
-        <v>0.229</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>891.438</v>
+        <v>135.745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="B4">
-        <v>0.051</v>
+        <v>0.099</v>
       </c>
       <c r="C4">
-        <v>4.731</v>
+        <v>3.87</v>
       </c>
       <c r="D4">
-        <v>0.549</v>
+        <v>0.58</v>
       </c>
       <c r="E4">
-        <v>0.464</v>
+        <v>0.364</v>
       </c>
       <c r="F4">
-        <v>0.626</v>
+        <v>0.952</v>
       </c>
       <c r="G4">
-        <v>1.679</v>
+        <v>1.69</v>
       </c>
       <c r="H4">
-        <v>0.734</v>
+        <v>0.646</v>
       </c>
       <c r="I4">
-        <v>0.285</v>
+        <v>0.335</v>
       </c>
       <c r="J4">
-        <v>6.784</v>
+        <v>6.143</v>
       </c>
       <c r="K4">
-        <v>0.466</v>
+        <v>0.528</v>
       </c>
       <c r="L4">
-        <v>3.598</v>
+        <v>3.204</v>
       </c>
       <c r="M4">
-        <v>1.674</v>
+        <v>1.042</v>
       </c>
       <c r="N4">
-        <v>0.585</v>
+        <v>1.846</v>
       </c>
       <c r="O4">
-        <v>1.057</v>
+        <v>5.237</v>
       </c>
       <c r="P4">
-        <v>2.056</v>
+        <v>9.092000000000001</v>
       </c>
       <c r="Q4">
-        <v>13.009</v>
+        <v>0.977</v>
       </c>
       <c r="R4">
-        <v>49.145</v>
+        <v>2.716</v>
       </c>
       <c r="S4">
-        <v>2.587</v>
+        <v>187.101</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>961.136</v>
       </c>
       <c r="U4">
-        <v>4.23</v>
+        <v>1194833.904</v>
       </c>
       <c r="V4">
-        <v>3.25</v>
+        <v>0.068</v>
       </c>
       <c r="W4">
-        <v>5.204</v>
+        <v>0.005</v>
       </c>
       <c r="X4">
-        <v>1355.654</v>
+        <v>30.571</v>
       </c>
       <c r="Y4">
-        <v>2256.569</v>
+        <v>5.079</v>
       </c>
       <c r="Z4">
-        <v>1240635.76</v>
+        <v>0.613</v>
       </c>
       <c r="AA4">
-        <v>0.013</v>
+        <v>70525.49000000001</v>
       </c>
       <c r="AB4">
-        <v>0.001</v>
+        <v>0.319</v>
       </c>
       <c r="AC4">
-        <v>8.239000000000001</v>
+        <v>65.779</v>
       </c>
       <c r="AD4">
-        <v>42.388</v>
+        <v>1.972</v>
       </c>
       <c r="AE4">
-        <v>7.076</v>
+        <v>35.431</v>
       </c>
       <c r="AF4">
-        <v>0.677</v>
+        <v>278.815</v>
       </c>
       <c r="AG4">
-        <v>185338.858</v>
+        <v>5.986</v>
       </c>
       <c r="AH4">
-        <v>0.183</v>
+        <v>0.119</v>
       </c>
       <c r="AI4">
-        <v>124.798</v>
+        <v>0.008</v>
       </c>
       <c r="AJ4">
-        <v>5.533</v>
+        <v>0.539</v>
       </c>
       <c r="AK4">
-        <v>197.674</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>2188.255</v>
-      </c>
-      <c r="AM4">
-        <v>6.954</v>
-      </c>
-      <c r="AN4">
-        <v>0.049</v>
-      </c>
-      <c r="AO4">
-        <v>0.016</v>
-      </c>
-      <c r="AP4">
-        <v>0.84</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>12.308</v>
+        <v>6.046</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.1</v>
+        <v>0.008</v>
       </c>
       <c r="B5">
-        <v>0.104</v>
+        <v>0.14</v>
       </c>
       <c r="C5">
-        <v>4.764</v>
+        <v>4.348</v>
       </c>
       <c r="D5">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="E5">
-        <v>0.297</v>
+        <v>0.242</v>
       </c>
       <c r="F5">
-        <v>1.212</v>
+        <v>1.753</v>
       </c>
       <c r="G5">
-        <v>0.737</v>
+        <v>0.844</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.122</v>
       </c>
       <c r="I5">
-        <v>0.288</v>
+        <v>0.4</v>
       </c>
       <c r="J5">
-        <v>6.008</v>
+        <v>5.475</v>
       </c>
       <c r="K5">
-        <v>0.423</v>
+        <v>0.51</v>
       </c>
       <c r="L5">
-        <v>1.324</v>
+        <v>1.198</v>
       </c>
       <c r="M5">
-        <v>1.75</v>
+        <v>1.226</v>
       </c>
       <c r="N5">
-        <v>0.432</v>
+        <v>5.376</v>
       </c>
       <c r="O5">
-        <v>1.261</v>
+        <v>6.671</v>
       </c>
       <c r="P5">
-        <v>9.443</v>
+        <v>8.06</v>
       </c>
       <c r="Q5">
-        <v>17.458</v>
+        <v>0.482</v>
       </c>
       <c r="R5">
-        <v>33.796</v>
+        <v>1.397</v>
       </c>
       <c r="S5">
-        <v>1.246</v>
+        <v>108.969</v>
       </c>
       <c r="T5">
-        <v>27.663</v>
+        <v>621.638</v>
       </c>
       <c r="U5">
-        <v>0.077</v>
+        <v>52995.731</v>
       </c>
       <c r="V5">
-        <v>0.06900000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="W5">
-        <v>0.082</v>
+        <v>0.223</v>
       </c>
       <c r="X5">
-        <v>939.22</v>
+        <v>8.231999999999999</v>
       </c>
       <c r="Y5">
-        <v>2792.597</v>
+        <v>0.555</v>
       </c>
       <c r="Z5">
-        <v>91326.143</v>
+        <v>0.01</v>
       </c>
       <c r="AA5">
-        <v>0.873</v>
+        <v>10228.582</v>
       </c>
       <c r="AB5">
-        <v>0.045</v>
+        <v>0.118</v>
       </c>
       <c r="AC5">
-        <v>7.183</v>
+        <v>19.006</v>
       </c>
       <c r="AD5">
-        <v>13.158</v>
+        <v>1.262</v>
       </c>
       <c r="AE5">
-        <v>0.436</v>
+        <v>52.229</v>
       </c>
       <c r="AF5">
-        <v>0.007</v>
+        <v>502.784</v>
       </c>
       <c r="AG5">
-        <v>27597.558</v>
+        <v>6.259</v>
       </c>
       <c r="AH5">
-        <v>0.08400000000000001</v>
+        <v>0.219</v>
       </c>
       <c r="AI5">
-        <v>50.646</v>
+        <v>0.168</v>
       </c>
       <c r="AJ5">
-        <v>3.706</v>
+        <v>0.078</v>
       </c>
       <c r="AK5">
-        <v>289.81</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>3817.629</v>
-      </c>
-      <c r="AM5">
-        <v>5.604</v>
-      </c>
-      <c r="AN5">
-        <v>0.106</v>
-      </c>
-      <c r="AO5">
-        <v>0.156</v>
-      </c>
-      <c r="AP5">
-        <v>0.121</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>4.813</v>
+        <v>3.663</v>
       </c>
     </row>
   </sheetData>
